--- a/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>JUANA ALARCO DE DAMMERT</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-7.15599</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.52316999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>348</v>
-      </c>
-      <c r="J2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-7.15599</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.52317</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>016 SARA MC DOUGALL</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-7.15147</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.52094</v>
-      </c>
-      <c r="I3" t="n">
-        <v>363</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-7.15147</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.52094</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>017</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-7.154227</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.512496</v>
-      </c>
-      <c r="I4" t="n">
-        <v>247</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-7.154227</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.512496</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>028 SANTA ELENA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-7.17017</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.51406</v>
-      </c>
-      <c r="I5" t="n">
-        <v>205</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-7.17017</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.51406</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>82641 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-7.1486</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.5248</v>
-      </c>
-      <c r="I6" t="n">
-        <v>597</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-7.1486</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.5248</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>82554 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-7.164764</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.503635</v>
-      </c>
-      <c r="I7" t="n">
-        <v>455</v>
-      </c>
-      <c r="J7" t="n">
-        <v>23</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-7.164764</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.503635</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>099</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-7.176125</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.508387</v>
-      </c>
-      <c r="I8" t="n">
-        <v>207</v>
-      </c>
-      <c r="J8" t="n">
-        <v>9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-7.176125</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.508387</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>HNO. VICTORINO ELORZ GOICOECHEA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-7.160513</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.511999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>488</v>
-      </c>
-      <c r="J9" t="n">
-        <v>27</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-7.160513</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.511999</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>105 PACHACUTEC</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-7.164583</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.521315</v>
-      </c>
-      <c r="I10" t="n">
-        <v>247</v>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-7.164583</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.521315</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>82022 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-7.11623</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.530176</v>
-      </c>
-      <c r="I11" t="n">
-        <v>388</v>
-      </c>
-      <c r="J11" t="n">
-        <v>23</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-7.11623</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.530176</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>82032</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-7.180377</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.481939</v>
-      </c>
-      <c r="I12" t="n">
-        <v>475</v>
-      </c>
-      <c r="J12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-7.180377</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.481939</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>183 MOLLEPAMPA BAJA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-7.185884</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.49508299999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>216</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-7.185884</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.495083</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>322</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-7.16904</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.5029</v>
-      </c>
-      <c r="I14" t="n">
-        <v>246</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-7.16904</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.5029</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>82001 SAN RAMON</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-7.153166</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-78.525021</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1850</v>
-      </c>
-      <c r="J15" t="n">
-        <v>59</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-7.153166</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.525021</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>82002 TARCISIO ZEGARRA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-7.15638</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.52287</v>
-      </c>
-      <c r="I16" t="n">
-        <v>578</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-7.15638</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.52287</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>82003 NUESTRA SEÑORA DE LA MERCED / NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-7.15643</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.52149</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1331</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-7.15643</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.52149</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>82004 ZULEMA ARCE SANTISTEBAN</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-7.154547</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.520625</v>
-      </c>
-      <c r="I18" t="n">
-        <v>800</v>
-      </c>
-      <c r="J18" t="n">
-        <v>31</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-7.154547</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.520625</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>82005</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-7.14621</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.523161</v>
-      </c>
-      <c r="I19" t="n">
-        <v>591</v>
-      </c>
-      <c r="J19" t="n">
-        <v>31</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-7.14621</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.523161</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>82008 / 82008 SANTA BEATRIZ DE SILVA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-7.144657</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-78.517864</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1065</v>
-      </c>
-      <c r="J20" t="n">
-        <v>54</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-7.144657</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-78.517864</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>82011</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-7.1477</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.51339</v>
-      </c>
-      <c r="I21" t="n">
-        <v>560</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-7.1477</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.51339</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>82012 / 82012 TORIBIO CASANOVA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-7.1543</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-78.51454</v>
-      </c>
-      <c r="I22" t="n">
-        <v>969</v>
-      </c>
-      <c r="J22" t="n">
-        <v>48</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-7.1543</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-78.51454</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>82015 RAFAEL OLASCOAGA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-7.145732</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.51105</v>
-      </c>
-      <c r="I23" t="n">
-        <v>785</v>
-      </c>
-      <c r="J23" t="n">
-        <v>43</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-7.145732</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.51105</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>EMBLEMATICO SANTA TERESITA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-7.156186</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.51235800000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2422</v>
-      </c>
-      <c r="J24" t="n">
-        <v>106</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-7.156186</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.512358</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>82019</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-7.16506</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.50949</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2199</v>
-      </c>
-      <c r="J25" t="n">
-        <v>97</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-7.16506</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.50949</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>82021</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-7.10525</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-78.553721</v>
-      </c>
-      <c r="I26" t="n">
-        <v>224</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-7.10525</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-78.553721</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>82029 SANTIAGO APOSTOL</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-7.220298</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-78.47036900000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>281</v>
-      </c>
-      <c r="J27" t="n">
-        <v>16</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-7.220298</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-78.470369</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>82031</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-7.190706</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-78.493403</v>
-      </c>
-      <c r="I28" t="n">
-        <v>578</v>
-      </c>
-      <c r="J28" t="n">
-        <v>28</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-7.190706</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-78.493403</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>82121</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-7.190911</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.503664</v>
-      </c>
-      <c r="I29" t="n">
-        <v>755</v>
-      </c>
-      <c r="J29" t="n">
-        <v>34</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-7.190911</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.503664</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>82594</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-7.16301</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.52007999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>513</v>
-      </c>
-      <c r="J30" t="n">
-        <v>25</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-7.16301</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.52008</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>821131</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-7.17078</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.51006</v>
-      </c>
-      <c r="I31" t="n">
-        <v>676</v>
-      </c>
-      <c r="J31" t="n">
-        <v>31</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-7.17078</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.51006</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>83003 SAN FRANCISCO</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-7.15354</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-78.52284</v>
-      </c>
-      <c r="I32" t="n">
-        <v>565</v>
-      </c>
-      <c r="J32" t="n">
-        <v>24</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-7.15354</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-78.52284</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>83004</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-7.159233</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-78.515546</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1009</v>
-      </c>
-      <c r="J33" t="n">
-        <v>46</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-7.159233</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-78.515546</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-7.149571</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-78.523111</v>
-      </c>
-      <c r="I34" t="n">
-        <v>896</v>
-      </c>
-      <c r="J34" t="n">
-        <v>41</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-7.149571</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-78.523111</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>RAFAEL LOAYZA GUEVARA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-7.152532</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-78.523878</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1139</v>
-      </c>
-      <c r="J35" t="n">
-        <v>66</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-7.152532</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-78.523878</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>JUAN XXIII</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-7.16242</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-78.51013</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1566</v>
-      </c>
-      <c r="J36" t="n">
-        <v>80</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-7.16242</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-78.51013</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-7.220092</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-78.471341</v>
-      </c>
-      <c r="I37" t="n">
-        <v>259</v>
-      </c>
-      <c r="J37" t="n">
-        <v>14</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-7.220092</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-78.471341</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>INDO AMERICANO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-7.1579</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-78.52321999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>74</v>
-      </c>
-      <c r="J38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-7.1579</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-78.52322</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>JOYAS PARA CRISTO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-7.15735</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-78.51378</v>
-      </c>
-      <c r="I39" t="n">
-        <v>372</v>
-      </c>
-      <c r="J39" t="n">
-        <v>30</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-7.15735</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-78.51378</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>ACUARELA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-7.15611</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-78.52095</v>
-      </c>
-      <c r="I40" t="n">
-        <v>204</v>
-      </c>
-      <c r="J40" t="n">
-        <v>18</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-7.15611</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-78.52095</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-7.15468</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-78.51607</v>
-      </c>
-      <c r="I41" t="n">
-        <v>370</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-7.15468</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-78.51607</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>EL CARMEN</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-7.14634</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-78.49339000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>625</v>
-      </c>
-      <c r="J42" t="n">
-        <v>38</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-7.14634</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-78.49339</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>DAVY</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-7.14634</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-78.49539</v>
-      </c>
-      <c r="I43" t="n">
-        <v>788</v>
-      </c>
-      <c r="J43" t="n">
-        <v>80</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-7.14634</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-78.49539</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>251 CORAZON DE MARIA / CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-7.16122</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-78.5256</v>
-      </c>
-      <c r="I44" t="n">
-        <v>579</v>
-      </c>
-      <c r="J44" t="n">
-        <v>29</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-7.16122</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-78.5256</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-7.17622</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-78.498575</v>
-      </c>
-      <c r="I45" t="n">
-        <v>871</v>
-      </c>
-      <c r="J45" t="n">
-        <v>37</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-7.17622</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-78.498575</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-7.1507</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-78.50274</v>
-      </c>
-      <c r="I46" t="n">
-        <v>517</v>
-      </c>
-      <c r="J46" t="n">
-        <v>45</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-7.1507</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-78.50274</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>82033</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-7.324211</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-78.51797000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>205</v>
-      </c>
-      <c r="J47" t="n">
-        <v>14</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-7.324211</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-78.51797</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>129 / 821136</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-7.11705</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-78.32414300000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>279</v>
-      </c>
-      <c r="J48" t="n">
-        <v>21</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-7.11705</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-78.324143</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>226 / 821005</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-6.863849</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-78.525535</v>
-      </c>
-      <c r="I49" t="n">
-        <v>91</v>
-      </c>
-      <c r="J49" t="n">
-        <v>7</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-6.863849</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-78.525535</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-7.029147</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-78.401673</v>
-      </c>
-      <c r="I50" t="n">
-        <v>222</v>
-      </c>
-      <c r="J50" t="n">
-        <v>22</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-7.029147</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-78.401673</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>82063</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-7.24699</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-78.378675</v>
-      </c>
-      <c r="I51" t="n">
-        <v>426</v>
-      </c>
-      <c r="J51" t="n">
-        <v>20</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-7.24699</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-78.378675</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>82064</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-7.248871</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-78.378618</v>
-      </c>
-      <c r="I52" t="n">
-        <v>251</v>
-      </c>
-      <c r="J52" t="n">
-        <v>15</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-7.248871</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-78.378618</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>DULCE NOMBRE DE JESUS</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-7.246203</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-78.382806</v>
-      </c>
-      <c r="I53" t="n">
-        <v>663</v>
-      </c>
-      <c r="J53" t="n">
-        <v>29</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-7.246203</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-78.382806</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-7.232231</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-78.41179099999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>286</v>
-      </c>
-      <c r="J54" t="n">
-        <v>18</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-7.232231</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-78.411791</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>82023</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-7.124212</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-78.45434899999999</v>
-      </c>
-      <c r="I55" t="n">
-        <v>516</v>
-      </c>
-      <c r="J55" t="n">
-        <v>22</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-7.124212</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-78.454349</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>82025</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-7.139625</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-78.481086</v>
-      </c>
-      <c r="I56" t="n">
-        <v>266</v>
-      </c>
-      <c r="J56" t="n">
-        <v>18</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-7.139625</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-78.481086</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>020</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-7.124902</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-78.455449</v>
-      </c>
-      <c r="I57" t="n">
-        <v>205</v>
-      </c>
-      <c r="J57" t="n">
-        <v>10</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-7.124902</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-78.455449</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>181</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-7.092186</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-78.521929</v>
-      </c>
-      <c r="I58" t="n">
-        <v>23</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-7.092186</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-78.521929</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>82024</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-7.128323</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-78.505636</v>
-      </c>
-      <c r="I59" t="n">
-        <v>312</v>
-      </c>
-      <c r="J59" t="n">
-        <v>17</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-7.128323</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-78.505636</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>82111</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-7.091933</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-78.521946</v>
-      </c>
-      <c r="I60" t="n">
-        <v>38</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-7.091933</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-78.521946</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>JESUS DE NAZARET</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-7.285083</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-78.577465</v>
-      </c>
-      <c r="I61" t="n">
-        <v>236</v>
-      </c>
-      <c r="J61" t="n">
-        <v>22</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-7.285083</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-78.577465</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>82076 SEGUNDO BRIONES VARGAS</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-7.2046</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-78.32380000000001</v>
-      </c>
-      <c r="I62" t="n">
-        <v>450</v>
-      </c>
-      <c r="J62" t="n">
-        <v>21</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-7.2046</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-78.3238</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>ANGELITOS DE DIOS</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-7.1794</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-78.50403</v>
-      </c>
-      <c r="I63" t="n">
-        <v>407</v>
-      </c>
-      <c r="J63" t="n">
-        <v>25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-7.1794</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-78.50403</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>SAN FERNANDO</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-7.16195</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-78.50394</v>
-      </c>
-      <c r="I64" t="n">
-        <v>923</v>
-      </c>
-      <c r="J64" t="n">
-        <v>29</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-7.16195</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-78.50394</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>ISAAC NEWTON</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-7.15825</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-78.51916</v>
-      </c>
-      <c r="I65" t="n">
-        <v>855</v>
-      </c>
-      <c r="J65" t="n">
-        <v>53</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-7.15825</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-78.51916</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>REY JOSIAS</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-7.171399</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-78.500699</v>
-      </c>
-      <c r="I66" t="n">
-        <v>48</v>
-      </c>
-      <c r="J66" t="n">
-        <v>4</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-7.171399</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-78.500699</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>SEGUNDO CABRERA MUÑOZ</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-7.16835</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-78.50543999999999</v>
-      </c>
-      <c r="I67" t="n">
-        <v>782</v>
-      </c>
-      <c r="J67" t="n">
-        <v>44</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-7.16835</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-78.50544</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>055 M ISABEL RODRIGUEZ URRUNAGA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-7.153928</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-78.522885</v>
-      </c>
-      <c r="I68" t="n">
-        <v>304</v>
-      </c>
-      <c r="J68" t="n">
-        <v>13</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-7.153928</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-78.522885</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>063</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-7.16108</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-78.51017</v>
-      </c>
-      <c r="I69" t="n">
-        <v>408</v>
-      </c>
-      <c r="J69" t="n">
-        <v>16</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-7.16108</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-78.51017</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>DIMAS SCHOOL</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-7.1613</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-78.51366</v>
-      </c>
-      <c r="I70" t="n">
-        <v>289</v>
-      </c>
-      <c r="J70" t="n">
-        <v>28</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-7.1613</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-78.51366</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>MONTE SION</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-7.18226</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-78.49229</v>
-      </c>
-      <c r="I71" t="n">
-        <v>498</v>
-      </c>
-      <c r="J71" t="n">
-        <v>30</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-7.18226</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-78.49229</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>JESUS CAUTIVO</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-7.16682</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-78.5038</v>
-      </c>
-      <c r="I72" t="n">
-        <v>222</v>
-      </c>
-      <c r="J72" t="n">
-        <v>14</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-7.16682</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-78.5038</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>DIEGO THOMSON BURNET</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-7.15343</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-78.51211000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>270</v>
-      </c>
-      <c r="J73" t="n">
-        <v>37</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-7.15343</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-78.51211</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>JULIO RAMON RIBEYRO</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-7.186634</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-78.489349</v>
-      </c>
-      <c r="I74" t="n">
-        <v>496</v>
-      </c>
-      <c r="J74" t="n">
-        <v>22</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-7.186634</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-78.489349</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>MARSHMELOW</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-7.14967</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-78.51622999999999</v>
-      </c>
-      <c r="I75" t="n">
-        <v>98</v>
-      </c>
-      <c r="J75" t="n">
-        <v>4</v>
-      </c>
-      <c r="K75" t="n">
-        <v>1</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-7.14967</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-78.51623</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>015 SANTA TERESITA</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-7.16166</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-78.512276</v>
-      </c>
-      <c r="I76" t="n">
-        <v>482</v>
-      </c>
-      <c r="J76" t="n">
-        <v>19</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-7.16166</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-78.512276</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>CRISTO RAMOS</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-7.086354</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-78.578841</v>
-      </c>
-      <c r="I77" t="n">
-        <v>409</v>
-      </c>
-      <c r="J77" t="n">
-        <v>21</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-7.086354</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-78.578841</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>83005</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-7.16206</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-78.511944</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1279</v>
-      </c>
-      <c r="J78" t="n">
-        <v>49</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-7.16206</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-78.511944</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>SAN RAMON</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-7.153202</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-78.523689</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2508</v>
-      </c>
-      <c r="J79" t="n">
-        <v>116</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-7.153202</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-78.523689</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>DOS DE MAYO</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-7.1651</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-78.51029</v>
-      </c>
-      <c r="I80" t="n">
-        <v>790</v>
-      </c>
-      <c r="J80" t="n">
-        <v>43</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-7.1651</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-78.51029</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>AULAS ABIERTAS VUELTA A LA ESCUELA</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-7.15446</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-78.50937</v>
-      </c>
-      <c r="I81" t="n">
-        <v>223</v>
-      </c>
-      <c r="J81" t="n">
-        <v>13</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-7.15446</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-78.50937</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>82949</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-7.16104</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-78.51215000000001</v>
-      </c>
-      <c r="I82" t="n">
-        <v>851</v>
-      </c>
-      <c r="J82" t="n">
-        <v>37</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-7.16104</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-78.51215</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>011</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-7.16537</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-78.50903</v>
-      </c>
-      <c r="I83" t="n">
-        <v>322</v>
-      </c>
-      <c r="J83" t="n">
-        <v>14</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-7.16537</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-78.50903</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>104 APLICACION</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-7.160553</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-78.51115799999999</v>
-      </c>
-      <c r="I84" t="n">
-        <v>313</v>
-      </c>
-      <c r="J84" t="n">
-        <v>14</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-7.160553</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-78.511158</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>SAN MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-7.16097</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-78.51188</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1446</v>
-      </c>
-      <c r="J85" t="n">
-        <v>62</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-7.16097</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-78.51188</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1446</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>081</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-7.14888</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-78.52478000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>258</v>
-      </c>
-      <c r="J86" t="n">
-        <v>13</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-7.14888</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-78.52478</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>WILLIAM PRESCOT</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-7.15205</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-78.50946999999999</v>
-      </c>
-      <c r="I87" t="n">
-        <v>401</v>
-      </c>
-      <c r="J87" t="n">
-        <v>21</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-7.15205</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-78.50947</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>ANGELES CELESTIALES</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-7.16735</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-78.51042</v>
-      </c>
-      <c r="I88" t="n">
-        <v>86</v>
-      </c>
-      <c r="J88" t="n">
-        <v>9</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-7.16735</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-78.51042</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>MONTE DEL HOREB COLLEGE</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-7.14825</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-78.51853</v>
-      </c>
-      <c r="I89" t="n">
-        <v>90</v>
-      </c>
-      <c r="J89" t="n">
-        <v>6</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-7.14825</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-78.51853</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>ALTAIR</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-7.146889</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-78.519611</v>
-      </c>
-      <c r="I90" t="n">
-        <v>454</v>
-      </c>
-      <c r="J90" t="n">
-        <v>24</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-7.146889</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-78.519611</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>JOHN F. KENNEDY COLLEGE</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-7.15768</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-78.51362</v>
-      </c>
-      <c r="I91" t="n">
-        <v>273</v>
-      </c>
-      <c r="J91" t="n">
-        <v>18</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-7.15768</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-78.51362</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>REAL COLLEGE</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-7.18533</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-78.503044</v>
-      </c>
-      <c r="I92" t="n">
-        <v>217</v>
-      </c>
-      <c r="J92" t="n">
-        <v>16</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-7.18533</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-78.503044</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>ARCOIRIS KIDS</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-7.171662</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-78.500551</v>
-      </c>
-      <c r="I93" t="n">
-        <v>26</v>
-      </c>
-      <c r="J93" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-7.171662</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-78.500551</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>INSPIRATION SCHOOLE</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-7.151681</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-78.507453</v>
-      </c>
-      <c r="I94" t="n">
-        <v>343</v>
-      </c>
-      <c r="J94" t="n">
-        <v>25</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-7.151681</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-78.507453</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>WEZ COLLEGE</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-7.20427</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-78.48199</v>
-      </c>
-      <c r="I95" t="n">
-        <v>204</v>
-      </c>
-      <c r="J95" t="n">
-        <v>20</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-7.20427</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-78.48199</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-7.15303</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-78.52245000000001</v>
-      </c>
-      <c r="I96" t="n">
-        <v>221</v>
-      </c>
-      <c r="J96" t="n">
-        <v>14</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-7.15303</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-78.52245</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>COAR CAJAMARCA</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-7.246221</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-78.382789</v>
-      </c>
-      <c r="I97" t="n">
-        <v>284</v>
-      </c>
-      <c r="J97" t="n">
-        <v>22</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-7.246221</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-78.382789</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>REY JOSIAS</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-7.171399</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-78.500699</v>
-      </c>
-      <c r="I98" t="n">
-        <v>120</v>
-      </c>
-      <c r="J98" t="n">
-        <v>7</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-7.171399</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-78.500699</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-7.16269</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-78.510367</v>
-      </c>
-      <c r="I99" t="n">
-        <v>900</v>
-      </c>
-      <c r="J99" t="n">
-        <v>50</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-7.16269</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-78.510367</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>HNO MIGUEL CARDUCCI RIPIANI</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-7.142036</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-78.524957</v>
-      </c>
-      <c r="I100" t="n">
-        <v>479</v>
-      </c>
-      <c r="J100" t="n">
-        <v>24</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-7.142036</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-78.524957</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>LA CATOLICA</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-7.15655</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-78.52043999999999</v>
-      </c>
-      <c r="I101" t="n">
-        <v>372</v>
-      </c>
-      <c r="J101" t="n">
-        <v>22</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-7.15655</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-78.52044</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>821228 EL INGENIO</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-7.146845</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-78.51524000000001</v>
-      </c>
-      <c r="I102" t="n">
-        <v>580</v>
-      </c>
-      <c r="J102" t="n">
-        <v>22</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-7.146845</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-78.51524</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>SAN ANDRES</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-7.16829</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-78.49343</v>
-      </c>
-      <c r="I103" t="n">
-        <v>681</v>
-      </c>
-      <c r="J103" t="n">
-        <v>37</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-7.16829</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-78.49343</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>CIENCIA Y TECNOLOGIA</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-7.14652</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-78.50752</v>
-      </c>
-      <c r="I104" t="n">
-        <v>591</v>
-      </c>
-      <c r="J104" t="n">
-        <v>38</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-7.14652</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-78.50752</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>REY JOSIAS</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-7.171399</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-78.500699</v>
-      </c>
-      <c r="I105" t="n">
-        <v>95</v>
-      </c>
-      <c r="J105" t="n">
-        <v>11</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-7.171399</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-78.500699</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>COLEGIO ADVENTISTA JOHN ANDREWS</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-7.15828</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-78.50335</v>
-      </c>
-      <c r="I106" t="n">
-        <v>487</v>
-      </c>
-      <c r="J106" t="n">
-        <v>33</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-7.15828</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-78.50335</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-7.15975</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-78.50667</v>
-      </c>
-      <c r="I107" t="n">
-        <v>217</v>
-      </c>
-      <c r="J107" t="n">
-        <v>11</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-7.15975</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-78.50667</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-7.157069</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-78.517521</v>
-      </c>
-      <c r="I108" t="n">
-        <v>229</v>
-      </c>
-      <c r="J108" t="n">
-        <v>14</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-7.157069</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-78.517521</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>JOSE MARIA ESCRIVA DE BALAGUER</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-7.151938</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-78.51026</v>
-      </c>
-      <c r="I109" t="n">
-        <v>324</v>
-      </c>
-      <c r="J109" t="n">
-        <v>18</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-7.151938</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-78.51026</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>93631</t>
+          <t>95017</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JUANA ALARCO DE DAMMERT</t>
+          <t>INDO AMERICANO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.15599</t>
+          <t>-7.1579</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.52317</t>
+          <t>-78.52322</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>93674</t>
+          <t>98389</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>016 SARA MC DOUGALL</t>
+          <t>020</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.15147</t>
+          <t>-7.124902</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.52094</t>
+          <t>-78.455449</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>93688</t>
+          <t>94211</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>EMBLEMATICO SANTA TERESITA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.154227</t>
+          <t>-7.156186</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.512496</t>
+          <t>-78.512358</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>93725</t>
+          <t>93688</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>028 SANTA ELENA</t>
+          <t>017</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.17017</t>
+          <t>-7.154227</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.51406</t>
+          <t>-78.512496</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>93792</t>
+          <t>94051</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>82641 SIMON BOLIVAR</t>
+          <t>322</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.1486</t>
+          <t>-7.16904</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.5248</t>
+          <t>-78.5029</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>847193</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>82554 INMACULADA CONCEPCION</t>
+          <t>REY JOSIAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.164764</t>
+          <t>-7.171399</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.503635</t>
+          <t>-78.500699</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>93834</t>
+          <t>859845</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.176125</t>
+          <t>-7.15975</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.508387</t>
+          <t>-78.50667</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>93853</t>
+          <t>570081</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HNO. VICTORINO ELORZ GOICOECHEA</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.160513</t>
+          <t>-7.153202</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.511999</t>
+          <t>-78.523689</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>93872</t>
+          <t>568832</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>82022 MICAELA BASTIDAS</t>
+          <t>055 M ISABEL RODRIGUEZ URRUNAGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.11623</t>
+          <t>-7.153928</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.530176</t>
+          <t>-78.522885</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>93928</t>
+          <t>570180</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>82032</t>
+          <t>AULAS ABIERTAS VUELTA A LA ESCUELA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.180377</t>
+          <t>-7.15446</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.481939</t>
+          <t>-78.50937</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>583446</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>183 MOLLEPAMPA BAJA</t>
+          <t>081</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.185884</t>
+          <t>-7.14888</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.495083</t>
+          <t>-78.52478</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>94051</t>
+          <t>93674</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>016 SARA MC DOUGALL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.16904</t>
+          <t>-7.15147</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.5029</t>
+          <t>-78.52094</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>363</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>94112</t>
+          <t>94249</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>82001 SAN RAMON</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.153166</t>
+          <t>-7.10525</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.525021</t>
+          <t>-78.553721</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>94131</t>
+          <t>94923</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>82002 TARCISIO ZEGARRA</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.15638</t>
+          <t>-7.220092</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.52287</t>
+          <t>-78.471341</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>94145</t>
+          <t>95574</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>82003 NUESTRA SEÑORA DE LA MERCED / NUESTRA SEÑORA DE LA MERCED</t>
+          <t>82033</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-7.15643</t>
+          <t>-7.324211</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.52149</t>
+          <t>-78.51797</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>569228</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>82004 ZULEMA ARCE SANTISTEBAN</t>
+          <t>JESUS CAUTIVO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.154547</t>
+          <t>-7.16682</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.520625</t>
+          <t>-78.5038</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>570444</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>82005</t>
+          <t>011</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.14621</t>
+          <t>-7.16537</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.523161</t>
+          <t>-78.50903</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>94174</t>
+          <t>570463</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>82008 / 82008 SANTA BEATRIZ DE SILVA</t>
+          <t>104 APLICACION</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.144657</t>
+          <t>-7.160553</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.517864</t>
+          <t>-78.511158</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>313</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>783370</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-7.1477</t>
+          <t>-7.15303</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.51339</t>
+          <t>-78.52245</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>94193</t>
+          <t>859850</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>82012 / 82012 TORIBIO CASANOVA</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.1543</t>
+          <t>-7.157069</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.51454</t>
+          <t>-78.517521</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>94206</t>
+          <t>97399</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>82015 RAFAEL OLASCOAGA</t>
+          <t>82064</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.145732</t>
+          <t>-7.248871</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.51105</t>
+          <t>-78.378618</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>94211</t>
+          <t>94268</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EMBLEMATICO SANTA TERESITA</t>
+          <t>82029 SANTIAGO APOSTOL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.156186</t>
+          <t>-7.220298</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.512358</t>
+          <t>-78.470369</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>94225</t>
+          <t>568969</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>82019</t>
+          <t>063</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-7.16506</t>
+          <t>-7.16108</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.50949</t>
+          <t>-78.51017</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>94249</t>
+          <t>691144</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>REAL COLLEGE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.10525</t>
+          <t>-7.18533</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.553721</t>
+          <t>-78.503044</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>94268</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>82029 SANTIAGO APOSTOL</t>
+          <t>82024</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.220298</t>
+          <t>-7.128323</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.470369</t>
+          <t>-78.505636</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>94287</t>
+          <t>93631</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>82031</t>
+          <t>JUANA ALARCO DE DAMMERT</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.190706</t>
+          <t>-7.15599</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.493403</t>
+          <t>-78.52317</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>94372</t>
+          <t>95140</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>82121</t>
+          <t>ACUARELA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.190911</t>
+          <t>-7.15611</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.503664</t>
+          <t>-78.52095</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>94433</t>
+          <t>97747</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>82594</t>
+          <t>JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7.16301</t>
+          <t>-7.232231</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.52008</t>
+          <t>-78.411791</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>94579</t>
+          <t>98025</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>821131</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-7.17078</t>
+          <t>-7.139625</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.51006</t>
+          <t>-78.481086</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>629246</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>83003 SAN FRANCISCO</t>
+          <t>JOHN F. KENNEDY COLLEGE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-7.15354</t>
+          <t>-7.15768</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.52284</t>
+          <t>-78.51362</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>94819</t>
+          <t>906309</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>JOSE MARIA ESCRIVA DE BALAGUER</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-7.159233</t>
+          <t>-7.151938</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.515546</t>
+          <t>-78.51026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>94881</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>015 SANTA TERESITA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.149571</t>
+          <t>-7.16166</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.523111</t>
+          <t>-78.512276</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>98431</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RAFAEL LOAYZA GUEVARA</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.152532</t>
+          <t>-7.092186</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.523878</t>
+          <t>-78.521929</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>94904</t>
+          <t>95159</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-7.16242</t>
+          <t>-7.15468</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.51013</t>
+          <t>-78.51607</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>94923</t>
+          <t>97380</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-7.220092</t>
+          <t>-7.24699</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.471341</t>
+          <t>-78.378675</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>426</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>95017</t>
+          <t>777618</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INDO AMERICANO</t>
+          <t>WEZ COLLEGE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-7.1579</t>
+          <t>-7.20427</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.52322</t>
+          <t>-78.48199</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>95041</t>
+          <t>96446</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JOYAS PARA CRISTO</t>
+          <t>129 / 821136</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-7.15735</t>
+          <t>-7.11705</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.51378</t>
+          <t>-78.324143</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>98978</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ACUARELA</t>
+          <t>82076 SEGUNDO BRIONES VARGAS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.15611</t>
+          <t>-7.2046</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.52095</t>
+          <t>-78.3238</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>95159</t>
+          <t>570019</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>RAMON CASTILLA</t>
+          <t>CRISTO RAMOS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-7.15468</t>
+          <t>-7.086354</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.51607</t>
+          <t>-78.578841</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>95164</t>
+          <t>601916</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EL CARMEN</t>
+          <t>WILLIAM PRESCOT</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-7.14634</t>
+          <t>-7.15205</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.49339</t>
+          <t>-78.50947</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>401</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>95178</t>
+          <t>97243</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DAVY</t>
+          <t>LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-7.14634</t>
+          <t>-7.029147</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.49539</t>
+          <t>-78.401673</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>95480</t>
+          <t>98011</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>251 CORAZON DE MARIA / CORAZON DE MARIA</t>
+          <t>82023</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-7.16122</t>
+          <t>-7.124212</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.5256</t>
+          <t>-78.454349</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>516</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>95499</t>
+          <t>98836</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>JESUS DE NAZARET</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-7.17622</t>
+          <t>-7.285083</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.498575</t>
+          <t>-78.577465</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>95531</t>
+          <t>569761</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-7.1507</t>
+          <t>-7.186634</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.50274</t>
+          <t>-78.489349</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>496</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>95574</t>
+          <t>784845</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>82033</t>
+          <t>COAR CAJAMARCA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-7.324211</t>
+          <t>-7.246221</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.51797</t>
+          <t>-78.382789</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>96446</t>
+          <t>815333</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>129 / 821136</t>
+          <t>LA CATOLICA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-7.11705</t>
+          <t>-7.15655</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-78.324143</t>
+          <t>-78.52044</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>96470</t>
+          <t>829330</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>226 / 821005</t>
+          <t>821228 EL INGENIO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.863849</t>
+          <t>-7.146845</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-78.525535</t>
+          <t>-78.51524</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>97243</t>
+          <t>93805</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO SANCHEZ</t>
+          <t>82554 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-7.029147</t>
+          <t>-7.164764</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-78.401673</t>
+          <t>-78.503635</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>97380</t>
+          <t>93872</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>82022 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-7.24699</t>
+          <t>-7.11623</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-78.378675</t>
+          <t>-78.530176</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>97399</t>
+          <t>94131</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>82064</t>
+          <t>82002 TARCISIO ZEGARRA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-7.248871</t>
+          <t>-7.15638</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-78.378618</t>
+          <t>-78.52287</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>578</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>97733</t>
+          <t>94188</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DULCE NOMBRE DE JESUS</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-7.246203</t>
+          <t>-7.1477</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-78.382806</t>
+          <t>-78.51339</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>560</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>97747</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JOSE OLAYA BALANDRA</t>
+          <t>83003 SAN FRANCISCO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-7.232231</t>
+          <t>-7.15354</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-78.411791</t>
+          <t>-78.52284</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>565</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>98011</t>
+          <t>628322</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>82023</t>
+          <t>ALTAIR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-7.124212</t>
+          <t>-7.146889</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-78.454349</t>
+          <t>-78.519611</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>454</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>98025</t>
+          <t>815045</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>HNO MIGUEL CARDUCCI RIPIANI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-7.139625</t>
+          <t>-7.142036</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-78.481086</t>
+          <t>-78.524957</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>98389</t>
+          <t>94433</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-7.124902</t>
+          <t>-7.16301</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-78.455449</t>
+          <t>-78.52008</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>513</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,37 +3973,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>98431</t>
+          <t>472778</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>ANGELITOS DE DIOS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-7.092186</t>
+          <t>-7.1794</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-78.521929</t>
+          <t>-78.50403</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>407</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>98493</t>
+          <t>775426</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>82024</t>
+          <t>INSPIRATION SCHOOLE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-7.128323</t>
+          <t>-7.151681</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-78.505636</t>
+          <t>-78.507453</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>98544</t>
+          <t>93928</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>82111</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-7.091933</t>
+          <t>-7.180377</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-78.521946</t>
+          <t>-78.481939</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>475</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>98836</t>
+          <t>93853</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARET</t>
+          <t>HNO. VICTORINO ELORZ GOICOECHEA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-7.285083</t>
+          <t>-7.160513</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-78.577465</t>
+          <t>-78.511999</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>488</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>98978</t>
+          <t>94287</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>82076 SEGUNDO BRIONES VARGAS</t>
+          <t>82031</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-7.2046</t>
+          <t>-7.190706</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-78.3238</t>
+          <t>-78.493403</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>578</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>472778</t>
+          <t>569148</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANGELITOS DE DIOS</t>
+          <t>DIMAS SCHOOL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-7.1794</t>
+          <t>-7.1613</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-78.50403</t>
+          <t>-78.51366</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,27 +4345,27 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>516452</t>
+          <t>95480</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SAN FERNANDO</t>
+          <t>251 CORAZON DE MARIA / CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-7.16195</t>
+          <t>-7.16122</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-78.50394</t>
+          <t>-78.5256</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>579</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>521646</t>
+          <t>97733</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>DULCE NOMBRE DE JESUS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-7.15825</t>
+          <t>-7.246203</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-78.51916</t>
+          <t>-78.382806</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>663</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>562707</t>
+          <t>516452</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>REY JOSIAS</t>
+          <t>SAN FERNANDO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-7.171399</t>
+          <t>-7.16195</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-78.500699</t>
+          <t>-78.50394</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>923</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>568808</t>
+          <t>98544</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SEGUNDO CABRERA MUÑOZ</t>
+          <t>82111</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-7.16835</t>
+          <t>-7.091933</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-78.50544</t>
+          <t>-78.521946</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>568832</t>
+          <t>756705</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>055 M ISABEL RODRIGUEZ URRUNAGA</t>
+          <t>ARCOIRIS KIDS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-7.153928</t>
+          <t>-7.171662</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-78.522885</t>
+          <t>-78.500551</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>568969</t>
+          <t>95041</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>JOYAS PARA CRISTO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-7.16108</t>
+          <t>-7.15735</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-78.51017</t>
+          <t>-78.51378</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>569148</t>
+          <t>569214</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DIMAS SCHOOL</t>
+          <t>MONTE SION</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-7.1613</t>
+          <t>-7.18226</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-78.51366</t>
+          <t>-78.49229</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>498</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>569214</t>
+          <t>93792</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MONTE SION</t>
+          <t>82641 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-7.18226</t>
+          <t>-7.1486</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-78.49229</t>
+          <t>-78.5248</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>597</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>569228</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JESUS CAUTIVO</t>
+          <t>82004 ZULEMA ARCE SANTISTEBAN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-7.16682</t>
+          <t>-7.154547</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-78.5038</t>
+          <t>-78.520625</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>569558</t>
+          <t>94169</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DIEGO THOMSON BURNET</t>
+          <t>82005</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-7.15343</t>
+          <t>-7.14621</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-78.51211</t>
+          <t>-78.523161</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>591</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>569761</t>
+          <t>94579</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JULIO RAMON RIBEYRO</t>
+          <t>821131</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-7.186634</t>
+          <t>-7.17078</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-78.489349</t>
+          <t>-78.51006</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>676</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,37 +5027,37 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>569799</t>
+          <t>856903</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MARSHMELOW</t>
+          <t>COLEGIO ADVENTISTA JOHN ANDREWS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-7.14967</t>
+          <t>-7.15828</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-78.51623</t>
+          <t>-78.50335</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>569803</t>
+          <t>94372</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>015 SANTA TERESITA</t>
+          <t>82121</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-7.16166</t>
+          <t>-7.190911</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-78.512276</t>
+          <t>-78.503664</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>755</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>570019</t>
+          <t>95499</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CRISTO RAMOS</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-7.086354</t>
+          <t>-7.17622</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-78.578841</t>
+          <t>-78.498575</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>570062</t>
+          <t>569558</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>83005</t>
+          <t>DIEGO THOMSON BURNET</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-7.16206</t>
+          <t>-7.15343</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-78.511944</t>
+          <t>-78.51211</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>570081</t>
+          <t>570401</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>82949</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-7.153202</t>
+          <t>-7.16104</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-78.523689</t>
+          <t>-78.51215</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>851</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>570104</t>
+          <t>834510</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>SAN ANDRES</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-7.1651</t>
+          <t>-7.16829</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-78.51029</t>
+          <t>-78.49343</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>570180</t>
+          <t>95164</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AULAS ABIERTAS VUELTA A LA ESCUELA</t>
+          <t>EL CARMEN</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-7.15446</t>
+          <t>-7.14634</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-78.50937</t>
+          <t>-78.49339</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>570401</t>
+          <t>839386</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>82949</t>
+          <t>CIENCIA Y TECNOLOGIA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-7.16104</t>
+          <t>-7.14652</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-78.51215</t>
+          <t>-78.50752</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>591</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>570444</t>
+          <t>562707</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>REY JOSIAS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-7.16537</t>
+          <t>-7.171399</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-78.50903</t>
+          <t>-78.500699</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,37 +5585,37 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>570463</t>
+          <t>569799</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>104 APLICACION</t>
+          <t>MARSHMELOW</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-7.160553</t>
+          <t>-7.14967</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-78.511158</t>
+          <t>-78.51623</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>98</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>570477</t>
+          <t>94881</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SAN MARCELINO CHAMPAGNAT</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-7.16097</t>
+          <t>-7.149571</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-78.51188</t>
+          <t>-78.523111</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>896</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>583446</t>
+          <t>94206</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>82015 RAFAEL OLASCOAGA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-7.14888</t>
+          <t>-7.145732</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-78.52478</t>
+          <t>-78.51105</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>785</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>601916</t>
+          <t>570104</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WILLIAM PRESCOT</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-7.15205</t>
+          <t>-7.1651</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-78.50947</t>
+          <t>-78.51029</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>790</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>607621</t>
+          <t>568808</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ANGELES CELESTIALES</t>
+          <t>SEGUNDO CABRERA MUÑOZ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-7.16735</t>
+          <t>-7.16835</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-78.51042</t>
+          <t>-78.50544</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>782</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,37 +5895,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>617267</t>
+          <t>95531</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MONTE DEL HOREB COLLEGE</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-7.14825</t>
+          <t>-7.1507</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-78.51853</t>
+          <t>-78.50274</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>517</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>628322</t>
+          <t>94819</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ALTAIR</t>
+          <t>83004</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-7.146889</t>
+          <t>-7.159233</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-78.519611</t>
+          <t>-78.515546</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>629246</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JOHN F. KENNEDY COLLEGE</t>
+          <t>82012 / 82012 TORIBIO CASANOVA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-7.15768</t>
+          <t>-7.1543</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-78.51362</t>
+          <t>-78.51454</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>969</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>691144</t>
+          <t>570062</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>REAL COLLEGE</t>
+          <t>83005</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-7.18533</t>
+          <t>-7.16206</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-78.503044</t>
+          <t>-78.511944</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>756705</t>
+          <t>805169</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ARCOIRIS KIDS</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-7.171662</t>
+          <t>-7.16269</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-78.500551</t>
+          <t>-78.510367</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>900</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>775426</t>
+          <t>521646</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>INSPIRATION SCHOOLE</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-7.151681</t>
+          <t>-7.15825</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-78.507453</t>
+          <t>-78.51916</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>855</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>777618</t>
+          <t>94145</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>WEZ COLLEGE</t>
+          <t>82003 NUESTRA SEÑORA DE LA MERCED / NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-7.20427</t>
+          <t>-7.15643</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-78.48199</t>
+          <t>-78.52149</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>783370</t>
+          <t>94174</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>82008 / 82008 SANTA BEATRIZ DE SILVA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-7.15303</t>
+          <t>-7.144657</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-78.52245</t>
+          <t>-78.517864</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>784845</t>
+          <t>94112</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>COAR CAJAMARCA</t>
+          <t>82001 SAN RAMON</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-7.246221</t>
+          <t>-7.153166</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-78.382789</t>
+          <t>-78.525021</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>803938</t>
+          <t>617267</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>REY JOSIAS</t>
+          <t>MONTE DEL HOREB COLLEGE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-7.171399</t>
+          <t>-7.14825</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-78.500699</t>
+          <t>-78.51853</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>805169</t>
+          <t>570477</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>SAN MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-7.16269</t>
+          <t>-7.16097</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-78.510367</t>
+          <t>-78.51188</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,37 +6577,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>815045</t>
+          <t>94895</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HNO MIGUEL CARDUCCI RIPIANI</t>
+          <t>RAFAEL LOAYZA GUEVARA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-7.142036</t>
+          <t>-7.152532</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-78.524957</t>
+          <t>-78.523878</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>815333</t>
+          <t>96470</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LA CATOLICA</t>
+          <t>226 / 821005</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-7.15655</t>
+          <t>-6.863849</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-78.52044</t>
+          <t>-78.525535</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6701,37 +6701,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>829330</t>
+          <t>803938</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>821228 EL INGENIO</t>
+          <t>REY JOSIAS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-7.146845</t>
+          <t>-7.171399</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-78.51524</t>
+          <t>-78.500699</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>94904</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SAN ANDRES</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-7.16829</t>
+          <t>-7.16242</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-78.49343</t>
+          <t>-78.51013</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>839386</t>
+          <t>95178</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CIENCIA Y TECNOLOGIA</t>
+          <t>DAVY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-7.14652</t>
+          <t>-7.14634</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-78.50752</t>
+          <t>-78.49539</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>788</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,37 +6887,37 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>847193</t>
+          <t>93725</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>REY JOSIAS</t>
+          <t>028 SANTA ELENA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-7.171399</t>
+          <t>-7.17017</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-78.500699</t>
+          <t>-78.51406</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>856903</t>
+          <t>93834</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>COLEGIO ADVENTISTA JOHN ANDREWS</t>
+          <t>099</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-7.15828</t>
+          <t>-7.176125</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-78.50335</t>
+          <t>-78.508387</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>859845</t>
+          <t>93952</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>183 MOLLEPAMPA BAJA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-7.15975</t>
+          <t>-7.185884</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-78.50667</t>
+          <t>-78.495083</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,37 +7073,37 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>859850</t>
+          <t>607621</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>ANGELES CELESTIALES</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-7.157069</t>
+          <t>-7.16735</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-78.517521</t>
+          <t>-78.51042</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>906309</t>
+          <t>94225</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JOSE MARIA ESCRIVA DE BALAGUER</t>
+          <t>82019</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-7.151938</t>
+          <t>-7.16506</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-78.51026</t>
+          <t>-78.50949</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>95017</t>
+          <t>906309</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>INDO AMERICANO</t>
+          <t>JOSE MARIA ESCRIVA DE BALAGUER</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.1579</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.52322</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-7.151938</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.51026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>98389</t>
+          <t>859850</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.124902</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.455449</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-7.157069</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.517521</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>94211</t>
+          <t>859845</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EMBLEMATICO SANTA TERESITA</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.156186</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.512358</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>-7.15975</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-78.50667</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>93688</t>
+          <t>856903</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>COLEGIO ADVENTISTA JOHN ANDREWS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.154227</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.512496</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-7.15828</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.50335</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>94051</t>
+          <t>847193</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>REY JOSIAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.16904</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.5029</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-7.171399</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.500699</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>847193</t>
+          <t>839386</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>REY JOSIAS</t>
+          <t>CIENCIA Y TECNOLOGIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.171399</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.500699</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>-7.14652</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.50752</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>859845</t>
+          <t>834510</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>SAN ANDRES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.15975</t>
+          <t>681</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.50667</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-7.16829</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.49343</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>570081</t>
+          <t>829330</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>821228 EL INGENIO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.153202</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.523689</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>-7.146845</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-78.51524</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>93867</t>
+          <t>815333</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105 PACHACUTEC</t>
+          <t>LA CATOLICA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.164583</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.521315</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-7.15655</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-78.52044</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>568832</t>
+          <t>815045</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>055 M ISABEL RODRIGUEZ URRUNAGA</t>
+          <t>HNO MIGUEL CARDUCCI RIPIANI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.153928</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.522885</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-7.142036</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.524957</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>570180</t>
+          <t>805169</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AULAS ABIERTAS VUELTA A LA ESCUELA</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.15446</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.50937</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>-7.16269</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.510367</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>583446</t>
+          <t>803938</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>REY JOSIAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.14888</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.52478</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-7.171399</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.500699</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>93674</t>
+          <t>784845</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>016 SARA MC DOUGALL</t>
+          <t>COAR CAJAMARCA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.15147</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.52094</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>-7.246221</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.382789</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>94249</t>
+          <t>783370</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.10525</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.553721</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-7.15303</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.52245</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>94923</t>
+          <t>777618</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>WEZ COLLEGE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.220092</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.471341</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-7.20427</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.48199</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>95574</t>
+          <t>775426</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>82033</t>
+          <t>INSPIRATION SCHOOLE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-7.324211</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.51797</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-7.151681</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.507453</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>569228</t>
+          <t>756705</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JESUS CAUTIVO</t>
+          <t>ARCOIRIS KIDS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.16682</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.5038</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-7.171662</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.500551</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>570444</t>
+          <t>691144</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>REAL COLLEGE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.16537</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.50903</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-7.18533</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.503044</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>570463</t>
+          <t>629246</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>104 APLICACION</t>
+          <t>JOHN F. KENNEDY COLLEGE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.160553</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.511158</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>-7.15768</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.51362</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>783370</t>
+          <t>628322</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>ALTAIR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-7.15303</t>
+          <t>454</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.52245</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-7.146889</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.519611</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>859850</t>
+          <t>617267</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>MONTE DEL HOREB COLLEGE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.157069</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.517521</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-7.14825</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.51853</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>97399</t>
+          <t>607621</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>82064</t>
+          <t>ANGELES CELESTIALES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.248871</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.378618</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-7.16735</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.51042</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>94268</t>
+          <t>601916</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>82029 SANTIAGO APOSTOL</t>
+          <t>WILLIAM PRESCOT</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.220298</t>
+          <t>401</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.470369</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-7.15205</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.50947</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>568969</t>
+          <t>583446</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>081</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-7.16108</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.51017</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>-7.14888</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.52478</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>691144</t>
+          <t>570477</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>REAL COLLEGE</t>
+          <t>SAN MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.18533</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.503044</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-7.16097</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-78.51188</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>98493</t>
+          <t>570463</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>82024</t>
+          <t>104 APLICACION</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.128323</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.505636</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-7.160553</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.511158</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>93631</t>
+          <t>570444</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JUANA ALARCO DE DAMMERT</t>
+          <t>011</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.15599</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.52317</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-7.16537</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.50903</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>95140</t>
+          <t>570401</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ACUARELA</t>
+          <t>82949</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.15611</t>
+          <t>851</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.52095</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-7.16104</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.51215</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>97747</t>
+          <t>570180</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JOSE OLAYA BALANDRA</t>
+          <t>AULAS ABIERTAS VUELTA A LA ESCUELA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7.232231</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.411791</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-7.15446</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.50937</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>98025</t>
+          <t>570104</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-7.139625</t>
+          <t>790</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.481086</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-7.1651</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.51029</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>629246</t>
+          <t>570081</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JOHN F. KENNEDY COLLEGE</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-7.15768</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.51362</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-7.153202</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.523689</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>906309</t>
+          <t>570062</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JOSE MARIA ESCRIVA DE BALAGUER</t>
+          <t>83005</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-7.151938</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.51026</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-7.16206</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.511944</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>569803</t>
+          <t>570019</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>015 SANTA TERESITA</t>
+          <t>CRISTO RAMOS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-7.16166</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.512276</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-7.086354</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.578841</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>98431</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>015 SANTA TERESITA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.092186</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.521929</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-7.16166</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-78.512276</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>95159</t>
+          <t>569799</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RAMON CASTILLA</t>
+          <t>MARSHMELOW</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-7.15468</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.51607</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-7.14967</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.51623</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>97380</t>
+          <t>569761</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-7.24699</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.378675</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>-7.186634</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.489349</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>777618</t>
+          <t>569558</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WEZ COLLEGE</t>
+          <t>DIEGO THOMSON BURNET</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-7.20427</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.48199</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-7.15343</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.51211</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>96446</t>
+          <t>569228</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>129 / 821136</t>
+          <t>JESUS CAUTIVO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-7.11705</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.324143</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-7.16682</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.5038</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>98978</t>
+          <t>569214</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>82076 SEGUNDO BRIONES VARGAS</t>
+          <t>MONTE SION</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.2046</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.3238</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>-7.18226</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.49229</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>570019</t>
+          <t>569148</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CRISTO RAMOS</t>
+          <t>DIMAS SCHOOL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-7.086354</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.578841</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>-7.1613</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.51366</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>601916</t>
+          <t>568969</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WILLIAM PRESCOT</t>
+          <t>063</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-7.15205</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.50947</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>-7.16108</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.51017</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>97243</t>
+          <t>568832</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO SANCHEZ</t>
+          <t>055 M ISABEL RODRIGUEZ URRUNAGA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-7.029147</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.401673</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-7.153928</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.522885</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>98011</t>
+          <t>568808</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>82023</t>
+          <t>SEGUNDO CABRERA MUÑOZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-7.124212</t>
+          <t>782</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.454349</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-7.16835</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.50544</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>98836</t>
+          <t>562707</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARET</t>
+          <t>REY JOSIAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-7.285083</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.577465</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-7.171399</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.500699</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>569761</t>
+          <t>521646</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JULIO RAMON RIBEYRO</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-7.186634</t>
+          <t>855</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.489349</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>-7.15825</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.51916</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>784845</t>
+          <t>516452</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>COAR CAJAMARCA</t>
+          <t>SAN FERNANDO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-7.246221</t>
+          <t>923</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.382789</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-7.16195</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.50394</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>815333</t>
+          <t>472778</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LA CATOLICA</t>
+          <t>ANGELITOS DE DIOS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-7.15655</t>
+          <t>407</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-78.52044</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-7.1794</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.50403</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>829330</t>
+          <t>098978</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>821228 EL INGENIO</t>
+          <t>82076 SEGUNDO BRIONES VARGAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-7.146845</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-78.51524</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>-7.2046</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.3238</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>098836</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>82554 INMACULADA CONCEPCION</t>
+          <t>JESUS DE NAZARET</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-7.164764</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-78.503635</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-7.285083</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.577465</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>93872</t>
+          <t>098544</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>82022 MICAELA BASTIDAS</t>
+          <t>82111</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-7.11623</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-78.530176</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-7.091933</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.521946</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>94131</t>
+          <t>098493</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>82002 TARCISIO ZEGARRA</t>
+          <t>82024</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-7.15638</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-78.52287</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-7.128323</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.505636</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>098431</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>82011</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-7.1477</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-78.51339</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>-7.092186</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.521929</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>098389</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>83003 SAN FRANCISCO</t>
+          <t>020</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-7.15354</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-78.52284</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>-7.124902</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.455449</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>628322</t>
+          <t>098025</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ALTAIR</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-7.146889</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-78.519611</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>-7.139625</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.481086</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>815045</t>
+          <t>098011</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HNO MIGUEL CARDUCCI RIPIANI</t>
+          <t>82023</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-7.142036</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-78.524957</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>-7.124212</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.454349</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>94433</t>
+          <t>097747</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>82594</t>
+          <t>JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-7.16301</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-78.52008</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>-7.232231</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.411791</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>472778</t>
+          <t>097733</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ANGELITOS DE DIOS</t>
+          <t>DULCE NOMBRE DE JESUS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-7.1794</t>
+          <t>663</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-78.50403</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>-7.246203</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.382806</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>775426</t>
+          <t>097399</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>INSPIRATION SCHOOLE</t>
+          <t>82064</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-7.151681</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-78.507453</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-7.248871</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-78.378618</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>93928</t>
+          <t>097380</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>82032</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-7.180377</t>
+          <t>426</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-78.481939</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>-7.24699</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.378675</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>93853</t>
+          <t>097243</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HNO. VICTORINO ELORZ GOICOECHEA</t>
+          <t>LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-7.160513</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-78.511999</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>-7.029147</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-78.401673</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>94287</t>
+          <t>096470</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>82031</t>
+          <t>226 / 821005</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-7.190706</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-78.493403</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-6.863849</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-78.525535</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>569148</t>
+          <t>096446</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DIMAS SCHOOL</t>
+          <t>129 / 821136</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-7.1613</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-78.51366</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-7.11705</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-78.324143</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>95480</t>
+          <t>095574</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>251 CORAZON DE MARIA / CORAZON DE MARIA</t>
+          <t>82033</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-7.16122</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-78.5256</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>-7.324211</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.51797</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>97733</t>
+          <t>095531</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DULCE NOMBRE DE JESUS</t>
+          <t>INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-7.246203</t>
+          <t>517</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-78.382806</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>-7.1507</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.50274</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>516452</t>
+          <t>095499</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAN FERNANDO</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-7.16195</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-78.50394</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>-7.17622</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.498575</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>98544</t>
+          <t>095480</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>82111</t>
+          <t>251 CORAZON DE MARIA / CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-7.091933</t>
+          <t>579</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-78.521946</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-7.16122</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.5256</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,37 +4593,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>756705</t>
+          <t>095178</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ARCOIRIS KIDS</t>
+          <t>DAVY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-7.171662</t>
+          <t>788</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-78.500551</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-7.14634</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.49539</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>95041</t>
+          <t>095164</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>JOYAS PARA CRISTO</t>
+          <t>EL CARMEN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-7.15735</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-78.51378</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-7.14634</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.49339</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>569214</t>
+          <t>095159</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MONTE SION</t>
+          <t>RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-7.18226</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-78.49229</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>-7.15468</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.51607</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>93792</t>
+          <t>095140</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>82641 SIMON BOLIVAR</t>
+          <t>ACUARELA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-7.1486</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-78.5248</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>-7.15611</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.52095</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>095041</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>82004 ZULEMA ARCE SANTISTEBAN</t>
+          <t>JOYAS PARA CRISTO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-7.154547</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-78.520625</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>-7.15735</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.51378</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>095017</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>82005</t>
+          <t>INDO AMERICANO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-7.14621</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-78.523161</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>-7.1579</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.52322</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>94579</t>
+          <t>094923</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>821131</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-7.17078</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-78.51006</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>-7.220092</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.471341</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>856903</t>
+          <t>094904</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>COLEGIO ADVENTISTA JOHN ANDREWS</t>
+          <t>JUAN XXIII</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-7.15828</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-78.50335</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-7.16242</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-78.51013</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,37 +5089,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>94372</t>
+          <t>094895</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>82121</t>
+          <t>RAFAEL LOAYZA GUEVARA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-7.190911</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-78.503664</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>-7.152532</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-78.523878</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>95499</t>
+          <t>094881</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-7.17622</t>
+          <t>896</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-78.498575</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>-7.149571</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.523111</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>569558</t>
+          <t>094819</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DIEGO THOMSON BURNET</t>
+          <t>83004</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-7.15343</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-78.51211</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-7.159233</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.515546</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>570401</t>
+          <t>094800</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>82949</t>
+          <t>83003 SAN FRANCISCO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-7.16104</t>
+          <t>565</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-78.51215</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>-7.15354</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.52284</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>094579</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAN ANDRES</t>
+          <t>821131</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-7.16829</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-78.49343</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>-7.17078</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.51006</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>95164</t>
+          <t>094433</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>EL CARMEN</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-7.14634</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-78.49339</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-7.16301</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-78.52008</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>839386</t>
+          <t>094372</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CIENCIA Y TECNOLOGIA</t>
+          <t>82121</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-7.14652</t>
+          <t>755</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-78.50752</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>-7.190911</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-78.503664</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>562707</t>
+          <t>094287</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>REY JOSIAS</t>
+          <t>82031</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-7.171399</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-78.500699</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-7.190706</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-78.493403</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,37 +5585,37 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>569799</t>
+          <t>094268</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MARSHMELOW</t>
+          <t>82029 SANTIAGO APOSTOL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-7.14967</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-78.51623</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>-7.220298</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-78.470369</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>94881</t>
+          <t>094249</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-7.149571</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-78.523111</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>-7.10525</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-78.553721</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>94206</t>
+          <t>094225</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>82015 RAFAEL OLASCOAGA</t>
+          <t>82019</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-7.145732</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-78.51105</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>-7.16506</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-78.50949</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>570104</t>
+          <t>094211</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>EMBLEMATICO SANTA TERESITA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-7.1651</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-78.51029</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>-7.156186</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-78.512358</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>568808</t>
+          <t>094206</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SEGUNDO CABRERA MUÑOZ</t>
+          <t>82015 RAFAEL OLASCOAGA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-7.16835</t>
+          <t>785</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-78.50544</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>-7.145732</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-78.51105</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>95531</t>
+          <t>094193</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>INMACULADA CONCEPCION</t>
+          <t>82012 / 82012 TORIBIO CASANOVA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-7.1507</t>
+          <t>969</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-78.50274</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>-7.1543</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-78.51454</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>94819</t>
+          <t>094188</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-7.159233</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-78.515546</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>-7.1477</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-78.51339</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>94193</t>
+          <t>094174</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>82012 / 82012 TORIBIO CASANOVA</t>
+          <t>82008 / 82008 SANTA BEATRIZ DE SILVA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-7.1543</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-78.51454</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>-7.144657</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-78.517864</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>570062</t>
+          <t>094169</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>83005</t>
+          <t>82005</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-7.16206</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-78.511944</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>-7.14621</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-78.523161</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>805169</t>
+          <t>094150</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>82004 ZULEMA ARCE SANTISTEBAN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-7.16269</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-78.510367</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>-7.154547</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-78.520625</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>521646</t>
+          <t>094145</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>82003 NUESTRA SEÑORA DE LA MERCED / NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-7.15825</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-78.51916</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>-7.15643</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-78.52149</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>94145</t>
+          <t>094131</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>82003 NUESTRA SEÑORA DE LA MERCED / NUESTRA SEÑORA DE LA MERCED</t>
+          <t>82002 TARCISIO ZEGARRA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-7.15643</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-78.52149</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>-7.15638</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-78.52287</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>94174</t>
+          <t>094112</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>82008 / 82008 SANTA BEATRIZ DE SILVA</t>
+          <t>82001 SAN RAMON</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-7.144657</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-78.517864</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>-7.153166</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-78.525021</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>94112</t>
+          <t>094051</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>82001 SAN RAMON</t>
+          <t>322</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-7.153166</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-78.525021</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>-7.16904</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-78.5029</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,37 +6453,37 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>617267</t>
+          <t>093952</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MONTE DEL HOREB COLLEGE</t>
+          <t>183 MOLLEPAMPA BAJA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-7.14825</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-78.51853</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-7.185884</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.495083</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>570477</t>
+          <t>093928</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAN MARCELINO CHAMPAGNAT</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-7.16097</t>
+          <t>475</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-78.51188</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>-7.180377</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-78.481939</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,37 +6577,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>093872</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RAFAEL LOAYZA GUEVARA</t>
+          <t>82022 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-7.152532</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-78.523878</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>-7.11623</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-78.530176</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>96470</t>
+          <t>093867</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>226 / 821005</t>
+          <t>105 PACHACUTEC</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-6.863849</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-78.525535</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-7.164583</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-78.521315</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6701,37 +6701,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>803938</t>
+          <t>093853</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>REY JOSIAS</t>
+          <t>HNO. VICTORINO ELORZ GOICOECHEA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-7.171399</t>
+          <t>488</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-78.500699</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>-7.160513</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-78.511999</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>94904</t>
+          <t>093834</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>JUAN XXIII</t>
+          <t>099</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-7.16242</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-78.51013</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>-7.176125</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-78.508387</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>95178</t>
+          <t>093805</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>DAVY</t>
+          <t>82554 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-7.14634</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-78.49539</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>-7.164764</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-78.503635</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>93725</t>
+          <t>093792</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>028 SANTA ELENA</t>
+          <t>82641 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-7.17017</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-78.51406</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-7.1486</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.5248</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>93834</t>
+          <t>093725</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>099</t>
+          <t>028 SANTA ELENA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-7.176125</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-78.508387</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-7.17017</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.51406</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7011,37 +7011,37 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>093688</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>183 MOLLEPAMPA BAJA</t>
+          <t>017</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-7.185884</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-78.495083</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-7.154227</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.512496</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7073,37 +7073,37 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>607621</t>
+          <t>093674</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ANGELES CELESTIALES</t>
+          <t>016 SARA MC DOUGALL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-7.16735</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-78.51042</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-7.15147</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.52094</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>94225</t>
+          <t>093631</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>82019</t>
+          <t>JUANA ALARCO DE DAMMERT</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-7.16506</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-78.50949</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>-7.15599</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-78.52317</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CAJAMARCA-CAJAMARCA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
